--- a/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
+++ b/StructureDefinition-mii-pr-seltene-clinical-diagnosis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$237</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9989" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9297" uniqueCount="855">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:15:21+00:00</t>
+    <t>2026-09-14T22:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1930,7 +1930,7 @@
     <t>Beginn</t>
   </si>
   <si>
-    <t>Geschätztes oder tatsächliches Datum oder Zeitraum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung begonnen hat.</t>
   </si>
   <si>
     <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
@@ -1970,428 +1970,105 @@
     <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod</t>
-  </si>
-  <si>
-    <t>onsetPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
+    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge</t>
+  </si>
+  <si>
+    <t>onsetAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
 </t>
   </si>
   <si>
-    <t>Beginn Zeitraum</t>
-  </si>
-  <si>
-    <t>Der Zeitraum, in dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.id</t>
+    <t>Erkrankungsbeginn als Alter</t>
+  </si>
+  <si>
+    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.id</t>
   </si>
   <si>
     <t>Condition.onset[x].id</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.extension</t>
+    <t>Condition.onset[x]:onsetAge.extension</t>
   </si>
   <si>
     <t>Condition.onset[x].extension</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von</t>
-  </si>
-  <si>
-    <t>lebensphase-von</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
+  </si>
+  <si>
+    <t>Lebensphase-Beginn</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://fhir.de/StructureDefinition/lebensphase}
 </t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.url</t>
+    <t>Lebensphase des Erkrankungsbeginns</t>
+  </si>
+  <si>
+    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.url</t>
   </si>
   <si>
     <t>http://fhir.de/StructureDefinition/lebensphase</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x]</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x]</t>
   </si>
   <si>
     <t>KlinischRelevanterZeitraum.Lebensphase.von</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Lebensphase</t>
   </si>
   <si>
     <t>http://fhir.de/ValueSet/lebensphase-de</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis</t>
-  </si>
-  <si>
-    <t>lebensphase-bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x]</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge</t>
-  </si>
-  <si>
-    <t>onsetAge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age
-</t>
-  </si>
-  <si>
-    <t>Erkrankungsbeginn als Alter</t>
-  </si>
-  <si>
-    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase des Erkrankungsbeginns</t>
-  </si>
-  <si>
-    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding.id</t>
@@ -2567,14 +2244,10 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>dateTime
-AgePeriodRangestring</t>
-  </si>
-  <si>
-    <t>When in resolution/remission</t>
-  </si>
-  <si>
-    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+    <t>Ende</t>
+  </si>
+  <si>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung beendet wurde.</t>
   </si>
   <si>
     <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
@@ -2585,6 +2258,177 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>Ende Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung beendet wurde.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge</t>
+  </si>
+  <si>
+    <t>abatementAge</t>
+  </si>
+  <si>
+    <t>Erkrankungsende als Alter</t>
+  </si>
+  <si>
+    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase des Erkrankungsendes</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x]</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].code</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -3034,98 +2878,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -3143,11 +2989,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ255"/>
+  <dimension ref="A1:AQ237"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="79.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.20703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.52734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3323,10 +3169,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -3406,7 +3252,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>81</v>
@@ -23616,7 +23462,7 @@
         <v>229</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>619</v>
@@ -23636,13 +23482,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>610</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>80</v>
@@ -23664,13 +23510,13 @@
         <v>93</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N167" t="s" s="2">
         <v>614</v>
@@ -23741,7 +23587,7 @@
         <v>80</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>631</v>
+        <v>80</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>619</v>
@@ -24003,14 +23849,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
         <v>636</v>
       </c>
       <c r="B170" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C170" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>80</v>
       </c>
@@ -24022,22 +23870,22 @@
         <v>92</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>228</v>
+        <v>638</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>639</v>
+        <v>378</v>
       </c>
       <c r="N170" t="s" s="2">
         <v>640</v>
@@ -24090,25 +23938,25 @@
         <v>80</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>641</v>
+        <v>119</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>642</v>
+        <v>80</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>643</v>
+        <v>80</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>80</v>
@@ -24117,7 +23965,7 @@
         <v>80</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>644</v>
+        <v>80</v>
       </c>
       <c r="AP170" t="s" s="2">
         <v>80</v>
@@ -24128,10 +23976,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24157,10 +24005,10 @@
         <v>106</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>647</v>
+        <v>107</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>648</v>
+        <v>108</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -24249,21 +24097,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>80</v>
@@ -24278,12 +24126,14 @@
         <v>112</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N172" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>80</v>
@@ -24322,7 +24172,9 @@
       <c r="AB172" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC172" s="2"/>
+      <c r="AC172" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="AD172" t="s" s="2">
         <v>80</v>
       </c>
@@ -24339,7 +24191,7 @@
         <v>82</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>120</v>
@@ -24368,20 +24220,18 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>652</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G173" t="s" s="2">
         <v>92</v>
@@ -24396,22 +24246,24 @@
         <v>80</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>653</v>
+        <v>133</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>377</v>
+        <v>206</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N173" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q173" s="2"/>
       <c r="R173" t="s" s="2">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="S173" t="s" s="2">
         <v>80</v>
@@ -24453,19 +24305,19 @@
         <v>80</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>80</v>
@@ -24489,12 +24341,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24502,13 +24354,13 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G174" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>80</v>
@@ -24517,13 +24369,13 @@
         <v>80</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -24574,7 +24426,7 @@
         <v>80</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -24583,16 +24435,16 @@
         <v>92</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>80</v>
+        <v>650</v>
       </c>
       <c r="AM174" t="s" s="2">
         <v>80</v>
@@ -24612,21 +24464,21 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>80</v>
@@ -24638,17 +24490,15 @@
         <v>80</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>80</v>
@@ -24685,31 +24535,31 @@
         <v>80</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>80</v>
@@ -24733,26 +24583,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>80</v>
@@ -24761,16 +24611,16 @@
         <v>80</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -24778,7 +24628,7 @@
       </c>
       <c r="Q176" s="2"/>
       <c r="R176" t="s" s="2">
-        <v>660</v>
+        <v>80</v>
       </c>
       <c r="S176" t="s" s="2">
         <v>80</v>
@@ -24808,31 +24658,31 @@
         <v>80</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>80</v>
@@ -24858,10 +24708,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24881,19 +24731,23 @@
         <v>80</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N177" s="2"/>
-      <c r="O177" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O177" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P177" t="s" s="2">
         <v>80</v>
       </c>
@@ -24917,13 +24771,13 @@
         <v>80</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>80</v>
+        <v>657</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>80</v>
+        <v>658</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>80</v>
@@ -24941,13 +24795,13 @@
         <v>80</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>199</v>
@@ -24959,7 +24813,7 @@
         <v>80</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>663</v>
+        <v>80</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>80</v>
@@ -24968,7 +24822,7 @@
         <v>80</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AP177" t="s" s="2">
         <v>80</v>
@@ -24979,10 +24833,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25100,10 +24954,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -25223,10 +25077,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25249,19 +25103,19 @@
         <v>93</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>80</v>
@@ -25286,13 +25140,13 @@
         <v>80</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>670</v>
+        <v>80</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>671</v>
+        <v>80</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>80</v>
@@ -25310,13 +25164,13 @@
         <v>80</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>199</v>
@@ -25337,7 +25191,7 @@
         <v>80</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>80</v>
@@ -25348,10 +25202,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25371,18 +25225,20 @@
         <v>80</v>
       </c>
       <c r="J181" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K181" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>107</v>
+        <v>276</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N181" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>80</v>
@@ -25431,7 +25287,7 @@
         <v>80</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>109</v>
+        <v>279</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -25440,10 +25296,10 @@
         <v>92</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>80</v>
@@ -25458,7 +25314,7 @@
         <v>80</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AP181" t="s" s="2">
         <v>80</v>
@@ -25467,46 +25323,48 @@
         <v>80</v>
       </c>
     </row>
-    <row r="182" hidden="true">
+    <row r="182">
       <c r="A182" t="s" s="2">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>113</v>
+        <v>282</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>114</v>
+        <v>283</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O182" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>80</v>
       </c>
@@ -25542,31 +25400,31 @@
         <v>80</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC182" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD182" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>119</v>
+        <v>285</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>199</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>80</v>
@@ -25581,7 +25439,7 @@
         <v>80</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="AP182" t="s" s="2">
         <v>80</v>
@@ -25590,12 +25448,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25603,13 +25461,13 @@
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>80</v>
@@ -25618,19 +25476,19 @@
         <v>93</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>271</v>
+        <v>399</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>80</v>
@@ -25679,7 +25537,7 @@
         <v>80</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -25706,7 +25564,7 @@
         <v>80</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="AP183" t="s" s="2">
         <v>80</v>
@@ -25717,10 +25575,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25743,18 +25601,20 @@
         <v>93</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O184" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>80</v>
       </c>
@@ -25802,7 +25662,7 @@
         <v>80</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25829,7 +25689,7 @@
         <v>80</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AP184" t="s" s="2">
         <v>80</v>
@@ -25838,12 +25698,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25851,13 +25711,13 @@
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G185" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>80</v>
@@ -25866,19 +25726,19 @@
         <v>93</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>167</v>
+        <v>106</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>399</v>
+        <v>304</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>80</v>
@@ -25927,7 +25787,7 @@
         <v>80</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25954,7 +25814,7 @@
         <v>80</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="AP185" t="s" s="2">
         <v>80</v>
@@ -25965,10 +25825,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25991,19 +25851,19 @@
         <v>93</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>106</v>
+        <v>677</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>288</v>
+        <v>678</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>289</v>
+        <v>679</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>399</v>
+        <v>680</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>290</v>
+        <v>681</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>80</v>
@@ -26052,7 +25912,7 @@
         <v>80</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>291</v>
+        <v>682</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -26061,7 +25921,7 @@
         <v>92</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>104</v>
@@ -26079,7 +25939,7 @@
         <v>80</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>292</v>
+        <v>683</v>
       </c>
       <c r="AP186" t="s" s="2">
         <v>80</v>
@@ -26110,30 +25970,30 @@
         <v>80</v>
       </c>
       <c r="I187" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J187" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>294</v>
+        <v>167</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>295</v>
+        <v>686</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="N187" s="2"/>
       <c r="O187" t="s" s="2">
-        <v>298</v>
+        <v>688</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q187" s="2"/>
+      <c r="Q187" t="s" s="2">
+        <v>689</v>
+      </c>
       <c r="R187" t="s" s="2">
         <v>80</v>
       </c>
@@ -26153,13 +26013,13 @@
         <v>80</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>80</v>
+        <v>690</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>80</v>
+        <v>691</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>80</v>
@@ -26177,7 +26037,7 @@
         <v>80</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>299</v>
+        <v>692</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -26186,7 +26046,7 @@
         <v>92</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>104</v>
@@ -26204,7 +26064,7 @@
         <v>80</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>300</v>
+        <v>693</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>80</v>
@@ -26215,10 +26075,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26244,16 +26104,14 @@
         <v>106</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>302</v>
+        <v>696</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>697</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" t="s" s="2">
-        <v>305</v>
+        <v>698</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>80</v>
@@ -26302,7 +26160,7 @@
         <v>80</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>306</v>
+        <v>699</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -26311,7 +26169,7 @@
         <v>92</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>104</v>
@@ -26329,7 +26187,7 @@
         <v>80</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>307</v>
+        <v>700</v>
       </c>
       <c r="AP188" t="s" s="2">
         <v>80</v>
@@ -26340,10 +26198,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>688</v>
+        <v>701</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26363,19 +26221,21 @@
         <v>80</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+      <c r="O189" t="s" s="2">
+        <v>705</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>80</v>
       </c>
@@ -26423,7 +26283,7 @@
         <v>80</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>692</v>
+        <v>706</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -26432,10 +26292,10 @@
         <v>92</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>80</v>
+        <v>707</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>80</v>
@@ -26450,7 +26310,7 @@
         <v>80</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>80</v>
@@ -26459,12 +26319,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>694</v>
+        <v>709</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26478,7 +26338,7 @@
         <v>92</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>80</v>
@@ -26487,24 +26347,24 @@
         <v>93</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>228</v>
+        <v>167</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O190" s="2"/>
+        <v>712</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>713</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q190" t="s" s="2">
-        <v>698</v>
-      </c>
+      <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
         <v>80</v>
       </c>
@@ -26548,7 +26408,7 @@
         <v>80</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>699</v>
+        <v>714</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -26557,7 +26417,7 @@
         <v>92</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>642</v>
+        <v>80</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>104</v>
@@ -26566,16 +26426,16 @@
         <v>80</v>
       </c>
       <c r="AL190" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM190" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN190" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO190" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>80</v>
@@ -26586,10 +26446,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26603,7 +26463,7 @@
         <v>92</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>80</v>
@@ -26612,15 +26472,17 @@
         <v>80</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>106</v>
+        <v>611</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>647</v>
+        <v>716</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N191" s="2"/>
+        <v>717</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>718</v>
+      </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>80</v>
@@ -26657,19 +26519,17 @@
         <v>80</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="AC191" s="2"/>
       <c r="AD191" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>109</v>
+        <v>715</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -26678,16 +26538,16 @@
         <v>92</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>80</v>
+        <v>719</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>80</v>
@@ -26699,20 +26559,22 @@
         <v>80</v>
       </c>
       <c r="AP191" t="s" s="2">
-        <v>80</v>
+        <v>720</v>
       </c>
       <c r="AQ191" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="192" hidden="true">
+    <row r="192">
       <c r="A192" t="s" s="2">
-        <v>704</v>
+        <v>721</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="C192" s="2"/>
+        <v>715</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="D192" t="s" s="2">
         <v>80</v>
       </c>
@@ -26721,10 +26583,10 @@
         <v>81</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H192" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I192" t="s" s="2">
         <v>80</v>
@@ -26733,15 +26595,17 @@
         <v>80</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>190</v>
+        <v>723</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N192" s="2"/>
+        <v>724</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>718</v>
+      </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>80</v>
@@ -26778,35 +26642,37 @@
         <v>80</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC192" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>119</v>
+        <v>715</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>80</v>
+        <v>719</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>80</v>
+        <v>725</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>80</v>
@@ -26818,7 +26684,7 @@
         <v>80</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>80</v>
+        <v>720</v>
       </c>
       <c r="AQ192" t="s" s="2">
         <v>80</v>
@@ -26826,13 +26692,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>705</v>
+        <v>715</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="D193" t="s" s="2">
         <v>80</v>
@@ -26854,15 +26720,17 @@
         <v>80</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>653</v>
+        <v>629</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>377</v>
+        <v>728</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N193" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>718</v>
+      </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>80</v>
@@ -26911,19 +26779,19 @@
         <v>80</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>119</v>
+        <v>715</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>199</v>
+        <v>719</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>80</v>
@@ -26941,7 +26809,7 @@
         <v>80</v>
       </c>
       <c r="AP193" t="s" s="2">
-        <v>80</v>
+        <v>720</v>
       </c>
       <c r="AQ193" t="s" s="2">
         <v>80</v>
@@ -26949,10 +26817,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>708</v>
+        <v>730</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>709</v>
+        <v>731</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -27070,10 +26938,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>710</v>
+        <v>732</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27084,7 +26952,7 @@
         <v>81</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>80</v>
@@ -27164,7 +27032,7 @@
         <v>82</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>120</v>
@@ -27191,26 +27059,28 @@
         <v>80</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>712</v>
+        <v>734</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C196" s="2"/>
+        <v>733</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>735</v>
+      </c>
       <c r="D196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G196" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H196" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I196" t="s" s="2">
         <v>80</v>
@@ -27219,16 +27089,16 @@
         <v>80</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>133</v>
+        <v>638</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>206</v>
+        <v>736</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>207</v>
+        <v>378</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>208</v>
+        <v>640</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -27236,7 +27106,7 @@
       </c>
       <c r="Q196" s="2"/>
       <c r="R196" t="s" s="2">
-        <v>660</v>
+        <v>80</v>
       </c>
       <c r="S196" t="s" s="2">
         <v>80</v>
@@ -27278,19 +27148,19 @@
         <v>80</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>210</v>
+        <v>119</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>80</v>
@@ -27314,12 +27184,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>714</v>
+        <v>737</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>715</v>
+        <v>738</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27327,13 +27197,13 @@
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G197" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>80</v>
@@ -27342,13 +27212,13 @@
         <v>80</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -27399,7 +27269,7 @@
         <v>80</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -27408,16 +27278,16 @@
         <v>92</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>716</v>
+        <v>80</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>80</v>
@@ -27437,21 +27307,21 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>717</v>
+        <v>739</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>80</v>
@@ -27463,15 +27333,17 @@
         <v>80</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N198" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>80</v>
@@ -27508,31 +27380,31 @@
         <v>80</v>
       </c>
       <c r="AB198" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC198" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE198" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>80</v>
@@ -27556,26 +27428,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="199" hidden="true">
+    <row r="199">
       <c r="A199" t="s" s="2">
-        <v>719</v>
+        <v>741</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>720</v>
+        <v>742</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H199" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I199" t="s" s="2">
         <v>80</v>
@@ -27584,16 +27456,16 @@
         <v>80</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>113</v>
+        <v>206</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
@@ -27601,7 +27473,7 @@
       </c>
       <c r="Q199" s="2"/>
       <c r="R199" t="s" s="2">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="S199" t="s" s="2">
         <v>80</v>
@@ -27631,31 +27503,31 @@
         <v>80</v>
       </c>
       <c r="AB199" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC199" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE199" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="AG199" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>80</v>
@@ -27681,10 +27553,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>721</v>
+        <v>743</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>722</v>
+        <v>744</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27704,23 +27576,19 @@
         <v>80</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>145</v>
+        <v>244</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>80</v>
       </c>
@@ -27744,13 +27612,13 @@
         <v>80</v>
       </c>
       <c r="X200" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>670</v>
+        <v>80</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>671</v>
+        <v>80</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>80</v>
@@ -27768,13 +27636,13 @@
         <v>80</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI200" t="s" s="2">
         <v>199</v>
@@ -27786,7 +27654,7 @@
         <v>80</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>80</v>
+        <v>745</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>80</v>
@@ -27795,7 +27663,7 @@
         <v>80</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>80</v>
@@ -27806,10 +27674,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>723</v>
+        <v>746</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27927,10 +27795,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>725</v>
+        <v>748</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>726</v>
+        <v>749</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28050,10 +27918,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>727</v>
+        <v>750</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>728</v>
+        <v>751</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28076,19 +27944,19 @@
         <v>93</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>80</v>
@@ -28113,13 +27981,13 @@
         <v>80</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>80</v>
+        <v>657</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>80</v>
+        <v>658</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>80</v>
@@ -28137,13 +28005,13 @@
         <v>80</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>199</v>
@@ -28164,7 +28032,7 @@
         <v>80</v>
       </c>
       <c r="AO203" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="AP203" t="s" s="2">
         <v>80</v>
@@ -28175,10 +28043,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>729</v>
+        <v>752</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>730</v>
+        <v>753</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -28198,20 +28066,18 @@
         <v>80</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K204" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>80</v>
@@ -28260,7 +28126,7 @@
         <v>80</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -28269,10 +28135,10 @@
         <v>92</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>80</v>
@@ -28287,7 +28153,7 @@
         <v>80</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="AP204" t="s" s="2">
         <v>80</v>
@@ -28296,48 +28162,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>731</v>
+        <v>754</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>732</v>
+        <v>755</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J205" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>282</v>
+        <v>113</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>283</v>
+        <v>114</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
         <v>80</v>
       </c>
@@ -28373,31 +28237,31 @@
         <v>80</v>
       </c>
       <c r="AB205" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC205" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE205" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>285</v>
+        <v>119</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>199</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK205" t="s" s="2">
         <v>80</v>
@@ -28412,7 +28276,7 @@
         <v>80</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>286</v>
+        <v>80</v>
       </c>
       <c r="AP205" t="s" s="2">
         <v>80</v>
@@ -28421,12 +28285,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="206" hidden="true">
+    <row r="206">
       <c r="A206" t="s" s="2">
-        <v>733</v>
+        <v>756</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>734</v>
+        <v>757</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28434,13 +28298,13 @@
       </c>
       <c r="E206" s="2"/>
       <c r="F206" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G206" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H206" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I206" t="s" s="2">
         <v>80</v>
@@ -28449,19 +28313,19 @@
         <v>93</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>399</v>
+        <v>271</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>80</v>
@@ -28510,7 +28374,7 @@
         <v>80</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -28537,7 +28401,7 @@
         <v>80</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>80</v>
@@ -28548,10 +28412,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>735</v>
+        <v>758</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28574,20 +28438,18 @@
         <v>93</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O207" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>80</v>
       </c>
@@ -28635,7 +28497,7 @@
         <v>80</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -28662,7 +28524,7 @@
         <v>80</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>80</v>
@@ -28671,12 +28533,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="208" hidden="true">
+    <row r="208">
       <c r="A208" t="s" s="2">
-        <v>737</v>
+        <v>760</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>738</v>
+        <v>761</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28684,13 +28546,13 @@
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G208" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>80</v>
@@ -28699,19 +28561,19 @@
         <v>93</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>304</v>
+        <v>399</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>80</v>
@@ -28760,7 +28622,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28787,7 +28649,7 @@
         <v>80</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>80</v>
@@ -28798,10 +28660,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>739</v>
+        <v>762</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28821,19 +28683,23 @@
         <v>80</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>228</v>
+        <v>106</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>690</v>
+        <v>288</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N209" s="2"/>
-      <c r="O209" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>80</v>
       </c>
@@ -28881,7 +28747,7 @@
         <v>80</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>692</v>
+        <v>291</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28890,10 +28756,10 @@
         <v>92</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>80</v>
@@ -28908,7 +28774,7 @@
         <v>80</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>80</v>
@@ -28917,16 +28783,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>741</v>
+        <v>764</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>742</v>
-      </c>
+        <v>765</v>
+      </c>
+      <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
         <v>80</v>
       </c>
@@ -28938,7 +28802,7 @@
         <v>92</v>
       </c>
       <c r="H210" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I210" t="s" s="2">
         <v>80</v>
@@ -28947,18 +28811,20 @@
         <v>93</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>743</v>
+        <v>294</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>744</v>
+        <v>295</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>745</v>
+        <v>296</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="O210" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>80</v>
       </c>
@@ -29006,7 +28872,7 @@
         <v>80</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>610</v>
+        <v>299</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -29015,7 +28881,7 @@
         <v>92</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ210" t="s" s="2">
         <v>104</v>
@@ -29027,16 +28893,16 @@
         <v>80</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>619</v>
+        <v>80</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO210" t="s" s="2">
-        <v>620</v>
+        <v>300</v>
       </c>
       <c r="AP210" t="s" s="2">
-        <v>621</v>
+        <v>80</v>
       </c>
       <c r="AQ210" t="s" s="2">
         <v>80</v>
@@ -29044,10 +28910,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>633</v>
+        <v>767</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -29067,19 +28933,23 @@
         <v>80</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K211" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N211" s="2"/>
-      <c r="O211" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N211" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O211" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P211" t="s" s="2">
         <v>80</v>
       </c>
@@ -29127,7 +28997,7 @@
         <v>80</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>109</v>
+        <v>306</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -29136,10 +29006,10 @@
         <v>92</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>80</v>
+        <v>199</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>80</v>
@@ -29154,7 +29024,7 @@
         <v>80</v>
       </c>
       <c r="AO211" t="s" s="2">
-        <v>80</v>
+        <v>307</v>
       </c>
       <c r="AP211" t="s" s="2">
         <v>80</v>
@@ -29165,21 +29035,21 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>635</v>
+        <v>769</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>80</v>
@@ -29188,21 +29058,23 @@
         <v>80</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>112</v>
+        <v>677</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>113</v>
+        <v>678</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>114</v>
+        <v>679</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O212" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="O212" t="s" s="2">
+        <v>681</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>80</v>
       </c>
@@ -29238,31 +29110,31 @@
         <v>80</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>119</v>
+        <v>682</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>80</v>
@@ -29277,7 +29149,7 @@
         <v>80</v>
       </c>
       <c r="AO212" t="s" s="2">
-        <v>80</v>
+        <v>683</v>
       </c>
       <c r="AP212" t="s" s="2">
         <v>80</v>
@@ -29288,14 +29160,12 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C213" t="s" s="2">
-        <v>749</v>
-      </c>
+        <v>771</v>
+      </c>
+      <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
         <v>80</v>
       </c>
@@ -29310,28 +29180,30 @@
         <v>80</v>
       </c>
       <c r="I213" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>653</v>
+        <v>167</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>750</v>
+        <v>686</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="O213" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="N213" s="2"/>
+      <c r="O213" t="s" s="2">
+        <v>688</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q213" s="2"/>
+      <c r="Q213" t="s" s="2">
+        <v>689</v>
+      </c>
       <c r="R213" t="s" s="2">
         <v>80</v>
       </c>
@@ -29351,13 +29223,13 @@
         <v>80</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>80</v>
+        <v>690</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>80</v>
+        <v>691</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>80</v>
@@ -29375,19 +29247,19 @@
         <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>119</v>
+        <v>692</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>80</v>
@@ -29402,7 +29274,7 @@
         <v>80</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>80</v>
+        <v>693</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>80</v>
@@ -29413,10 +29285,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29436,19 +29308,21 @@
         <v>80</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K214" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>107</v>
+        <v>696</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>108</v>
+        <v>697</v>
       </c>
       <c r="N214" s="2"/>
-      <c r="O214" s="2"/>
+      <c r="O214" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="P214" t="s" s="2">
         <v>80</v>
       </c>
@@ -29496,7 +29370,7 @@
         <v>80</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>109</v>
+        <v>699</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -29508,7 +29382,7 @@
         <v>80</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>80</v>
@@ -29523,7 +29397,7 @@
         <v>80</v>
       </c>
       <c r="AO214" t="s" s="2">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AP214" t="s" s="2">
         <v>80</v>
@@ -29534,21 +29408,21 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>80</v>
@@ -29557,21 +29431,21 @@
         <v>80</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>113</v>
+        <v>703</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O215" s="2"/>
+        <v>704</v>
+      </c>
+      <c r="N215" s="2"/>
+      <c r="O215" t="s" s="2">
+        <v>705</v>
+      </c>
       <c r="P215" t="s" s="2">
         <v>80</v>
       </c>
@@ -29607,31 +29481,31 @@
         <v>80</v>
       </c>
       <c r="AB215" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC215" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD215" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE215" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>119</v>
+        <v>706</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>199</v>
+        <v>707</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>80</v>
@@ -29646,7 +29520,7 @@
         <v>80</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>80</v>
@@ -29655,12 +29529,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29668,39 +29542,41 @@
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G216" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H216" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I216" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J216" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I216" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J216" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K216" t="s" s="2">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>206</v>
+        <v>710</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>207</v>
+        <v>711</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>712</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>713</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q216" s="2"/>
       <c r="R216" t="s" s="2">
-        <v>660</v>
+        <v>80</v>
       </c>
       <c r="S216" t="s" s="2">
         <v>80</v>
@@ -29742,10 +29618,10 @@
         <v>80</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>210</v>
+        <v>714</v>
       </c>
       <c r="AG216" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH216" t="s" s="2">
         <v>92</v>
@@ -29754,7 +29630,7 @@
         <v>80</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>80</v>
@@ -29769,7 +29645,7 @@
         <v>80</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>80</v>
@@ -29780,10 +29656,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29803,16 +29679,16 @@
         <v>80</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>214</v>
+        <v>779</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>215</v>
+        <v>780</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -29863,7 +29739,7 @@
         <v>80</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>216</v>
+        <v>778</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -29872,7 +29748,7 @@
         <v>92</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ217" t="s" s="2">
         <v>104</v>
@@ -29881,7 +29757,7 @@
         <v>80</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>80</v>
+        <v>781</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>80</v>
@@ -29890,21 +29766,21 @@
         <v>80</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>80</v>
+        <v>782</v>
       </c>
       <c r="AP217" t="s" s="2">
-        <v>80</v>
+        <v>783</v>
       </c>
       <c r="AQ217" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="218" hidden="true">
+    <row r="218">
       <c r="A218" t="s" s="2">
-        <v>760</v>
+        <v>784</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>761</v>
+        <v>784</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29918,22 +29794,22 @@
         <v>92</v>
       </c>
       <c r="H218" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I218" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>106</v>
+        <v>785</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>107</v>
+        <v>786</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>108</v>
+        <v>787</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -29984,7 +29860,7 @@
         <v>80</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>109</v>
+        <v>784</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -29996,7 +29872,7 @@
         <v>80</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>80</v>
@@ -30014,51 +29890,49 @@
         <v>80</v>
       </c>
       <c r="AP218" t="s" s="2">
-        <v>80</v>
+        <v>788</v>
       </c>
       <c r="AQ218" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="219" hidden="true">
+    <row r="219">
       <c r="A219" t="s" s="2">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>763</v>
+        <v>789</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>112</v>
+        <v>785</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>113</v>
+        <v>790</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N219" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>791</v>
+      </c>
+      <c r="N219" s="2"/>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>80</v>
@@ -30095,31 +29969,31 @@
         <v>80</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC219" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE219" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>119</v>
+        <v>789</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>80</v>
@@ -30134,10 +30008,10 @@
         <v>80</v>
       </c>
       <c r="AO219" t="s" s="2">
-        <v>80</v>
+        <v>792</v>
       </c>
       <c r="AP219" t="s" s="2">
-        <v>80</v>
+        <v>793</v>
       </c>
       <c r="AQ219" t="s" s="2">
         <v>80</v>
@@ -30145,10 +30019,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>764</v>
+        <v>794</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>765</v>
+        <v>794</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -30156,10 +30030,10 @@
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>93</v>
@@ -30168,23 +30042,19 @@
         <v>80</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>145</v>
+        <v>795</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>260</v>
+        <v>796</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O220" t="s" s="2">
-        <v>263</v>
-      </c>
+        <v>797</v>
+      </c>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
         <v>80</v>
       </c>
@@ -30208,13 +30078,13 @@
         <v>80</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>670</v>
+        <v>80</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>671</v>
+        <v>80</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>80</v>
@@ -30232,7 +30102,7 @@
         <v>80</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>264</v>
+        <v>794</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -30241,10 +30111,10 @@
         <v>82</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>104</v>
+        <v>798</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>80</v>
@@ -30259,7 +30129,7 @@
         <v>80</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="AP220" t="s" s="2">
         <v>80</v>
@@ -30270,10 +30140,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>766</v>
+        <v>799</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30391,10 +30261,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>768</v>
+        <v>800</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>769</v>
+        <v>800</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30464,16 +30334,16 @@
         <v>80</v>
       </c>
       <c r="AB222" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AC222" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AD222" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE222" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AF222" t="s" s="2">
         <v>119</v>
@@ -30485,7 +30355,7 @@
         <v>82</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>120</v>
@@ -30512,47 +30382,47 @@
         <v>80</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>770</v>
+        <v>801</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>771</v>
+        <v>801</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
-        <v>80</v>
+        <v>802</v>
       </c>
       <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H223" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I223" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="I223" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J223" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>269</v>
+        <v>803</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>270</v>
+        <v>804</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>80</v>
@@ -30601,19 +30471,19 @@
         <v>80</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>273</v>
+        <v>805</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH223" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK223" t="s" s="2">
         <v>80</v>
@@ -30628,7 +30498,7 @@
         <v>80</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>80</v>
@@ -30639,10 +30509,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>772</v>
+        <v>806</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>773</v>
+        <v>806</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -30662,20 +30532,18 @@
         <v>80</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>276</v>
+        <v>807</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>808</v>
+      </c>
+      <c r="N224" s="2"/>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
         <v>80</v>
@@ -30700,13 +30568,13 @@
         <v>80</v>
       </c>
       <c r="X224" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Y224" t="s" s="2">
-        <v>80</v>
+        <v>809</v>
       </c>
       <c r="Z224" t="s" s="2">
-        <v>80</v>
+        <v>810</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>80</v>
@@ -30724,7 +30592,7 @@
         <v>80</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>279</v>
+        <v>806</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -30733,7 +30601,7 @@
         <v>92</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>199</v>
+        <v>811</v>
       </c>
       <c r="AJ224" t="s" s="2">
         <v>104</v>
@@ -30748,10 +30616,10 @@
         <v>80</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>80</v>
+        <v>812</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="AP224" t="s" s="2">
         <v>80</v>
@@ -30762,10 +30630,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>774</v>
+        <v>813</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>775</v>
+        <v>813</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30773,10 +30641,10 @@
       </c>
       <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>93</v>
@@ -30785,23 +30653,19 @@
         <v>80</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>167</v>
+        <v>814</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>282</v>
+        <v>815</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="N225" s="2"/>
+      <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>80</v>
       </c>
@@ -30849,16 +30713,16 @@
         <v>80</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>285</v>
+        <v>813</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>199</v>
+        <v>811</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>104</v>
@@ -30876,7 +30740,7 @@
         <v>80</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>286</v>
+        <v>80</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>80</v>
@@ -30885,12 +30749,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="226" hidden="true">
+    <row r="226">
       <c r="A226" t="s" s="2">
-        <v>776</v>
+        <v>817</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>777</v>
+        <v>817</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30904,29 +30768,25 @@
         <v>92</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>288</v>
+        <v>818</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O226" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="N226" s="2"/>
+      <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>80</v>
       </c>
@@ -30950,13 +30810,13 @@
         <v>80</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>80</v>
+        <v>820</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>80</v>
+        <v>821</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>80</v>
@@ -30974,7 +30834,7 @@
         <v>80</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>291</v>
+        <v>817</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -30983,7 +30843,7 @@
         <v>92</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ226" t="s" s="2">
         <v>104</v>
@@ -31001,7 +30861,7 @@
         <v>80</v>
       </c>
       <c r="AO226" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="AP226" t="s" s="2">
         <v>80</v>
@@ -31010,12 +30870,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="227" hidden="true">
+    <row r="227">
       <c r="A227" t="s" s="2">
-        <v>778</v>
+        <v>822</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>779</v>
+        <v>822</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -31026,32 +30886,30 @@
         <v>81</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H227" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I227" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>294</v>
+        <v>795</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>295</v>
+        <v>823</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>296</v>
+        <v>824</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O227" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>825</v>
+      </c>
+      <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
         <v>80</v>
       </c>
@@ -31099,19 +30957,19 @@
         <v>80</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>299</v>
+        <v>822</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH227" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>104</v>
+        <v>826</v>
       </c>
       <c r="AK227" t="s" s="2">
         <v>80</v>
@@ -31126,7 +30984,7 @@
         <v>80</v>
       </c>
       <c r="AO227" t="s" s="2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="AP227" t="s" s="2">
         <v>80</v>
@@ -31137,10 +30995,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>780</v>
+        <v>827</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>781</v>
+        <v>827</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -31160,23 +31018,19 @@
         <v>80</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K228" t="s" s="2">
         <v>106</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N228" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N228" s="2"/>
+      <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
         <v>80</v>
       </c>
@@ -31224,7 +31078,7 @@
         <v>80</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -31233,10 +31087,10 @@
         <v>92</v>
       </c>
       <c r="AI228" t="s" s="2">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>80</v>
@@ -31251,7 +31105,7 @@
         <v>80</v>
       </c>
       <c r="AO228" t="s" s="2">
-        <v>307</v>
+        <v>80</v>
       </c>
       <c r="AP228" t="s" s="2">
         <v>80</v>
@@ -31262,21 +31116,21 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>782</v>
+        <v>828</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>783</v>
+        <v>828</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>80</v>
@@ -31285,23 +31139,21 @@
         <v>80</v>
       </c>
       <c r="J229" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>784</v>
+        <v>112</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>785</v>
+        <v>113</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>786</v>
+        <v>114</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>788</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
         <v>80</v>
       </c>
@@ -31349,19 +31201,19 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>789</v>
+        <v>119</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK229" t="s" s="2">
         <v>80</v>
@@ -31376,7 +31228,7 @@
         <v>80</v>
       </c>
       <c r="AO229" t="s" s="2">
-        <v>790</v>
+        <v>80</v>
       </c>
       <c r="AP229" t="s" s="2">
         <v>80</v>
@@ -31387,21 +31239,21 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>791</v>
+        <v>829</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>80</v>
+        <v>802</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>80</v>
@@ -31413,24 +31265,24 @@
         <v>93</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="N230" s="2"/>
+        <v>804</v>
+      </c>
+      <c r="N230" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O230" t="s" s="2">
-        <v>795</v>
+        <v>233</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q230" t="s" s="2">
-        <v>796</v>
-      </c>
+      <c r="Q230" s="2"/>
       <c r="R230" t="s" s="2">
         <v>80</v>
       </c>
@@ -31450,13 +31302,13 @@
         <v>80</v>
       </c>
       <c r="X230" t="s" s="2">
-        <v>248</v>
+        <v>80</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>797</v>
+        <v>80</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>798</v>
+        <v>80</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>80</v>
@@ -31474,19 +31326,19 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK230" t="s" s="2">
         <v>80</v>
@@ -31501,7 +31353,7 @@
         <v>80</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>80</v>
@@ -31510,12 +31362,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="231" hidden="true">
+    <row r="231">
       <c r="A231" t="s" s="2">
-        <v>801</v>
+        <v>830</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>802</v>
+        <v>830</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31526,10 +31378,10 @@
         <v>81</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H231" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I231" t="s" s="2">
         <v>80</v>
@@ -31538,18 +31390,16 @@
         <v>93</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>803</v>
+        <v>831</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>804</v>
+        <v>832</v>
       </c>
       <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>805</v>
-      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>80</v>
       </c>
@@ -31573,13 +31423,13 @@
         <v>80</v>
       </c>
       <c r="X231" t="s" s="2">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="Y231" t="s" s="2">
-        <v>80</v>
+        <v>833</v>
       </c>
       <c r="Z231" t="s" s="2">
-        <v>80</v>
+        <v>834</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>80</v>
@@ -31597,37 +31447,37 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>806</v>
+        <v>830</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>80</v>
+        <v>835</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="AL231" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>80</v>
+        <v>836</v>
       </c>
       <c r="AN231" t="s" s="2">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>807</v>
+        <v>80</v>
       </c>
       <c r="AP231" t="s" s="2">
-        <v>80</v>
+        <v>837</v>
       </c>
       <c r="AQ231" t="s" s="2">
         <v>80</v>
@@ -31635,10 +31485,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>809</v>
+        <v>838</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31658,21 +31508,19 @@
         <v>80</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>810</v>
+        <v>107</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>811</v>
+        <v>108</v>
       </c>
       <c r="N232" s="2"/>
-      <c r="O232" t="s" s="2">
-        <v>812</v>
-      </c>
+      <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
         <v>80</v>
       </c>
@@ -31720,7 +31568,7 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>813</v>
+        <v>109</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -31729,10 +31577,10 @@
         <v>92</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>814</v>
+        <v>80</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK232" t="s" s="2">
         <v>80</v>
@@ -31747,7 +31595,7 @@
         <v>80</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>807</v>
+        <v>80</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>80</v>
@@ -31758,21 +31606,21 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>815</v>
+        <v>839</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>816</v>
+        <v>839</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>80</v>
@@ -31781,23 +31629,21 @@
         <v>80</v>
       </c>
       <c r="J233" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>817</v>
+        <v>113</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>818</v>
+        <v>114</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>820</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
         <v>80</v>
       </c>
@@ -31833,31 +31679,31 @@
         <v>80</v>
       </c>
       <c r="AB233" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AC233" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AD233" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE233" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>821</v>
+        <v>119</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI233" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>80</v>
@@ -31872,7 +31718,7 @@
         <v>80</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>807</v>
+        <v>80</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>80</v>
@@ -31881,12 +31727,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31897,30 +31743,32 @@
         <v>81</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H234" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I234" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J234" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J234" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K234" t="s" s="2">
-        <v>823</v>
+        <v>145</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>824</v>
+        <v>260</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>825</v>
+        <v>261</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="O234" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O234" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P234" t="s" s="2">
         <v>80</v>
       </c>
@@ -31944,13 +31792,11 @@
         <v>80</v>
       </c>
       <c r="X234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>80</v>
+        <v>512</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>80</v>
@@ -31968,16 +31814,16 @@
         <v>80</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>822</v>
+        <v>264</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH234" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>827</v>
+        <v>80</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>104</v>
@@ -31995,21 +31841,21 @@
         <v>80</v>
       </c>
       <c r="AO234" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="AP234" t="s" s="2">
-        <v>828</v>
+        <v>80</v>
       </c>
       <c r="AQ234" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -32017,13 +31863,13 @@
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G235" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H235" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I235" t="s" s="2">
         <v>80</v>
@@ -32032,16 +31878,20 @@
         <v>93</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>228</v>
+        <v>106</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>830</v>
+        <v>302</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="N235" s="2"/>
-      <c r="O235" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N235" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O235" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P235" t="s" s="2">
         <v>80</v>
       </c>
@@ -32089,7 +31939,7 @@
         <v>80</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>829</v>
+        <v>306</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -32107,7 +31957,7 @@
         <v>80</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>832</v>
+        <v>80</v>
       </c>
       <c r="AM235" t="s" s="2">
         <v>80</v>
@@ -32116,10 +31966,10 @@
         <v>80</v>
       </c>
       <c r="AO235" t="s" s="2">
-        <v>833</v>
+        <v>307</v>
       </c>
       <c r="AP235" t="s" s="2">
-        <v>834</v>
+        <v>80</v>
       </c>
       <c r="AQ235" t="s" s="2">
         <v>80</v>
@@ -32127,10 +31977,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -32141,7 +31991,7 @@
         <v>81</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>93</v>
@@ -32153,15 +32003,17 @@
         <v>93</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="N236" s="2"/>
+        <v>845</v>
+      </c>
+      <c r="N236" t="s" s="2">
+        <v>846</v>
+      </c>
       <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>80</v>
@@ -32210,22 +32062,22 @@
         <v>80</v>
       </c>
       <c r="AF236" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="AG236" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH236" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI236" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="AG236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH236" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI236" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>80</v>
+        <v>847</v>
       </c>
       <c r="AL236" t="s" s="2">
         <v>80</v>
@@ -32240,7 +32092,7 @@
         <v>80</v>
       </c>
       <c r="AP236" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AQ236" t="s" s="2">
         <v>80</v>
@@ -32248,10 +32100,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -32262,7 +32114,7 @@
         <v>81</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>93</v>
@@ -32271,16 +32123,16 @@
         <v>80</v>
       </c>
       <c r="J237" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>836</v>
+        <v>849</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -32331,13 +32183,13 @@
         <v>80</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>80</v>
@@ -32349,2228 +32201,26 @@
         <v>80</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>80</v>
+        <v>852</v>
       </c>
       <c r="AM237" t="s" s="2">
-        <v>80</v>
+        <v>853</v>
       </c>
       <c r="AN237" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO237" t="s" s="2">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="AP237" t="s" s="2">
-        <v>844</v>
+        <v>80</v>
       </c>
       <c r="AQ237" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="C238" s="2"/>
-      <c r="D238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E238" s="2"/>
-      <c r="F238" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G238" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H238" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K238" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="L238" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="N238" s="2"/>
-      <c r="O238" s="2"/>
-      <c r="P238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q238" s="2"/>
-      <c r="R238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF238" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="AG238" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH238" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ238" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="AK238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ238" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="239" hidden="true">
-      <c r="A239" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="C239" s="2"/>
-      <c r="D239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E239" s="2"/>
-      <c r="F239" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G239" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K239" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L239" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N239" s="2"/>
-      <c r="O239" s="2"/>
-      <c r="P239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q239" s="2"/>
-      <c r="R239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF239" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG239" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH239" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ239" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="240" hidden="true">
-      <c r="A240" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="C240" s="2"/>
-      <c r="D240" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E240" s="2"/>
-      <c r="F240" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G240" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K240" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L240" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O240" s="2"/>
-      <c r="P240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q240" s="2"/>
-      <c r="R240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG240" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH240" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ240" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ240" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="241" hidden="true">
-      <c r="A241" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="C241" s="2"/>
-      <c r="D241" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="E241" s="2"/>
-      <c r="F241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G241" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L241" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="P241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q241" s="2"/>
-      <c r="R241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ241" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="242" hidden="true">
-      <c r="A242" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="C242" s="2"/>
-      <c r="D242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E242" s="2"/>
-      <c r="F242" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G242" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K242" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="L242" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N242" s="2"/>
-      <c r="O242" s="2"/>
-      <c r="P242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q242" s="2"/>
-      <c r="R242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X242" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y242" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="Z242" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="AA242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF242" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="AG242" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH242" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI242" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="AJ242" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN242" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="AO242" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AP242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ242" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="C243" s="2"/>
-      <c r="D243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E243" s="2"/>
-      <c r="F243" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G243" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H243" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K243" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="L243" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="N243" s="2"/>
-      <c r="O243" s="2"/>
-      <c r="P243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q243" s="2"/>
-      <c r="R243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ243" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G244" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H244" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K244" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="L244" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="M244" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="N244" s="2"/>
-      <c r="O244" s="2"/>
-      <c r="P244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q244" s="2"/>
-      <c r="R244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X244" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y244" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="Z244" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="AA244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF244" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="AG244" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH244" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ244" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ244" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="C245" s="2"/>
-      <c r="D245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E245" s="2"/>
-      <c r="F245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G245" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H245" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K245" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="L245" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="M245" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="O245" s="2"/>
-      <c r="P245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q245" s="2"/>
-      <c r="R245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF245" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="AG245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH245" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ245" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="AK245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ245" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="246" hidden="true">
-      <c r="A246" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="C246" s="2"/>
-      <c r="D246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E246" s="2"/>
-      <c r="F246" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G246" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K246" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L246" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M246" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N246" s="2"/>
-      <c r="O246" s="2"/>
-      <c r="P246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q246" s="2"/>
-      <c r="R246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF246" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG246" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH246" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ246" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="247" hidden="true">
-      <c r="A247" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="C247" s="2"/>
-      <c r="D247" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E247" s="2"/>
-      <c r="F247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G247" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K247" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L247" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M247" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N247" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O247" s="2"/>
-      <c r="P247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q247" s="2"/>
-      <c r="R247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF247" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH247" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ247" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ247" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="248" hidden="true">
-      <c r="A248" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="C248" s="2"/>
-      <c r="D248" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G248" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I248" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="J248" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K248" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L248" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="M248" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="N248" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O248" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="P248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q248" s="2"/>
-      <c r="R248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF248" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="AG248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH248" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ248" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ248" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="C249" s="2"/>
-      <c r="D249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E249" s="2"/>
-      <c r="F249" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G249" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H249" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J249" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K249" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="L249" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="N249" s="2"/>
-      <c r="O249" s="2"/>
-      <c r="P249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q249" s="2"/>
-      <c r="R249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X249" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y249" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="Z249" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="AA249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF249" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="AG249" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH249" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI249" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="AJ249" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK249" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AL249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM249" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="AN249" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AO249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP249" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="AQ249" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="250" hidden="true">
-      <c r="A250" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="C250" s="2"/>
-      <c r="D250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E250" s="2"/>
-      <c r="F250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G250" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K250" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L250" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N250" s="2"/>
-      <c r="O250" s="2"/>
-      <c r="P250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q250" s="2"/>
-      <c r="R250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF250" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AG250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH250" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ250" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="251" hidden="true">
-      <c r="A251" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="C251" s="2"/>
-      <c r="D251" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="E251" s="2"/>
-      <c r="F251" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G251" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K251" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L251" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="M251" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N251" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O251" s="2"/>
-      <c r="P251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q251" s="2"/>
-      <c r="R251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB251" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC251" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AD251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE251" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF251" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG251" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH251" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ251" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ251" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="252" hidden="true">
-      <c r="A252" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="D252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E252" s="2"/>
-      <c r="F252" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G252" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J252" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K252" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="L252" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="M252" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N252" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O252" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="P252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q252" s="2"/>
-      <c r="R252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X252" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y252" s="2"/>
-      <c r="Z252" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AA252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF252" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AG252" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH252" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ252" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO252" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AP252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ252" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="253" hidden="true">
-      <c r="A253" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="C253" s="2"/>
-      <c r="D253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E253" s="2"/>
-      <c r="F253" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G253" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="H253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J253" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K253" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L253" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M253" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N253" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O253" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q253" s="2"/>
-      <c r="R253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF253" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG253" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH253" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ253" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO253" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AP253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ253" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="C254" s="2"/>
-      <c r="D254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E254" s="2"/>
-      <c r="F254" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G254" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H254" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J254" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="K254" t="s" s="2">
-        <v>894</v>
-      </c>
-      <c r="L254" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="M254" t="s" s="2">
-        <v>896</v>
-      </c>
-      <c r="N254" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="O254" s="2"/>
-      <c r="P254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q254" s="2"/>
-      <c r="R254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF254" t="s" s="2">
-        <v>893</v>
-      </c>
-      <c r="AG254" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH254" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI254" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="AJ254" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK254" t="s" s="2">
-        <v>898</v>
-      </c>
-      <c r="AL254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP254" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="AQ254" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="C255" s="2"/>
-      <c r="D255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E255" s="2"/>
-      <c r="F255" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G255" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H255" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="I255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K255" t="s" s="2">
-        <v>900</v>
-      </c>
-      <c r="L255" t="s" s="2">
-        <v>901</v>
-      </c>
-      <c r="M255" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="N255" s="2"/>
-      <c r="O255" s="2"/>
-      <c r="P255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q255" s="2"/>
-      <c r="R255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF255" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="AG255" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH255" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ255" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL255" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="AM255" t="s" s="2">
-        <v>904</v>
-      </c>
-      <c r="AN255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO255" t="s" s="2">
-        <v>905</v>
-      </c>
-      <c r="AP255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ255" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ255">
+  <autoFilter ref="A1:AQ237">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -34580,7 +32230,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI254">
+  <conditionalFormatting sqref="A2:AI236">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
